--- a/CardamomOT_inputs.xlsx
+++ b/CardamomOT_inputs.xlsx
@@ -11,13 +11,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="model_parameters" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gene_lists" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stimulus_inference_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stimulus_simulation_schedule" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="perturbation_inference" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="perturbation_simulation" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="times" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="proliferation_rates" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="population_sizes" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="transition_rates" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stimulus_test_schedule" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stimulus_simulation_schedule" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="perturbation_inference" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="perturbation_simulation" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="times" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="proliferation_rates" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="population_sizes" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="transition_rates" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -198,6 +199,26 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
+        <t>Timepoint</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Total population size at this timepoint</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment11.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CardamomOT</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
         <t>Source cell type (rows) and target cell types (header): allowed transition rates</t>
       </text>
     </comment>
@@ -243,10 +264,15 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
+        <t>Optional: dataset_id whose schedule these rows replace (empty or "all": default schedule of every sample)</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
         <t>Timepoint (optional: without times, rows follow the sorted timepoints of the data)</t>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <t>Value of stimulus 1 at this timepoint (default: 0 at the first timepoint, 1 after)</t>
       </text>
@@ -263,17 +289,17 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Simulated timepoint (optional: without times, rows follow the sorted simulated timepoints)</t>
+        <t>Optional: dataset_id whose schedule these rows replace (empty or "all": default)</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Inference stimulus 1 during the simulations (default: its inference schedule)</t>
+        <t>Timepoint (optional: without times, rows follow the sorted timepoints)</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Perturbation stimulus STIM1 of perturbation_simulation (default: 0 at the first time, 1 after)</t>
+        <t>Value of inference stimulus 1 for the held-out cells (default: the inference schedule)</t>
       </text>
     </comment>
   </commentList>
@@ -288,32 +314,22 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>dataset_id of a measured sample carrying genetic perturbations (KO / OV), or "all" for the row describing the inference stimuli (STIMk / RATEk)</t>
+        <t>Optional: dataset_id whose schedule these rows replace (empty or "all": default)</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Genes knocked-out in this sample, comma-separated</t>
+        <t>Simulated timepoint (optional: without times, rows follow the sorted simulated timepoints)</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Genes over-expressed in this sample, comma-separated</t>
+        <t>Inference stimulus 1 during the simulations (default: its inference schedule)</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Row "all": possible direct targets of inference stimulus 1: a gene list of gene_lists or comma-separated genes (empty: every gene)</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>Row "all": effect of inference stimulus 1 on the net proliferation rate (per hour), TARGET:delta comma-separated, scaled by its schedule: TARGET = a cell type of cell_type_proliferation (delta added to its rate of proliferation_rates, which is then the rate without stimulus), or a gene list of gene_lists / GENE1+GENE2 / a gene (delta x mRNA signature score in [0, 1])</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>Free comment (ignored)</t>
+        <t>Perturbation stimulus STIM1 of perturbation_simulation (default: 0 at the first time, 1 after)</t>
       </text>
     </comment>
   </commentList>
@@ -328,25 +344,40 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Knocked-out genes, comma-separated; GENE-X for a partial KO of X%</t>
+        <t>dataset_id of a measured sample carrying genetic perturbations (KO / OV), or "all" for the row describing the inference stimuli (STIMk / RATEk)</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Over-expressed genes, comma-separated; GENE-X for a partial OV of X%</t>
+        <t>Genes knocked-out in this sample, comma-separated</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Perturbation stimulus 1: targets followed by + (activated) or - (inhibited), e.g. CHGA+STMN2-</t>
+        <t>Genes over-expressed in this sample, comma-separated</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Effect of stimulus 1 (its schedule, STIM1 may be empty) on the net proliferation rate: TARGET:delta, comma-separated; TARGET = a gene list of gene_lists, GENE1+GENE2..., a gene or 'all'; delta (per time unit) added to R of a cell at the maximal score, e.g. ferroptosis_sensitive:-0.01 (needs the proliferation MLP)</t>
+        <t>True / 1: every cell of this sample is held out (data_test, not split), excluded from the gene selection and the inference; infer_test validates the model on it with its stimulus_test_schedule</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Removed sample without the first timepoint: dataset_id whose first-timepoint training cells start its validation simulation</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Row "all": possible direct targets of inference stimulus 1: a gene list of gene_lists or comma-separated genes (empty: every gene)</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Row "all": effect of inference stimulus 1 on the net proliferation rate (per hour), TARGET:delta comma-separated, scaled by its schedule: TARGET = a cell type of cell_type_proliferation (delta added to its rate of proliferation_rates, which is then the rate without stimulus), or a gene list of gene_lists / GENE1+GENE2 / a gene (delta x mRNA signature score in [0, 1])</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <t>Free comment (ignored)</t>
       </text>
@@ -363,12 +394,27 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Inference restricted to the timepoints &lt;= the largest value of this column</t>
+        <t>Knocked-out genes, comma-separated; GENE-X for a partial KO of X%</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Timepoints of the simulations (0 added if absent)</t>
+        <t>Over-expressed genes, comma-separated; GENE-X for a partial OV of X%</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Perturbation stimulus 1: targets followed by + (activated) or - (inhibited), e.g. CHGA+STMN2-</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Effect of stimulus 1 (its schedule, STIM1 may be empty) on the net proliferation rate: TARGET:delta, comma-separated; TARGET = a gene list of gene_lists, GENE1+GENE2..., a gene or 'all'; delta (per time unit) added to R of a cell at the maximal score, e.g. ferroptosis_sensitive:-0.01 (needs the proliferation MLP)</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Free comment (ignored)</t>
       </text>
     </comment>
   </commentList>
@@ -383,12 +429,12 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Cell type (as in obs cell_type_proliferation, else cell_type_transition, else cell_type)</t>
+        <t>Inference restricted to the timepoints &lt;= the largest value of this column</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Reference net proliferation rate (birth - death), in h^-1; without the inference stimulus if perturbation_inference gives its effect on this cell type (RATEk)</t>
+        <t>Timepoints of the simulations (0 added if absent)</t>
       </text>
     </comment>
   </commentList>
@@ -403,12 +449,12 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Timepoint</t>
+        <t>Cell type (as in obs cell_type_proliferation, else cell_type_transition, else cell_type)</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Total population size at this timepoint</t>
+        <t>Reference net proliferation rate (birth - death), in h^-1; without the inference stimulus if perturbation_inference gives its effect on this cell type (RATEk)</t>
       </text>
     </comment>
   </commentList>
@@ -704,7 +750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -798,7 +844,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Schedule of the stimuli of the measured data (inference); one row per timepoint, one column per stimulus (add stimulus_2, stimulus_3... for several stimuli; without this sheet: one stimulus).</t>
+          <t>Schedule of the stimuli of the measured data (inference); one row per timepoint, one column per stimulus (add stimulus_2, stimulus_3... for several stimuli; without this sheet: one stimulus). Rows with a sample_id give the schedule of that sample only (e.g. an untreated control at 0).</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -810,117 +856,130 @@
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>stimulus_simulation_schedule</t>
+          <t>stimulus_test_schedule</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Schedules of the simulations, one row per simulated timepoint: inference stimuli (stimulus_k, acting on the genes and, through the RATEk of perturbation_inference, on proliferation and death), then perturbation stimuli (STIMk, as in perturbation_simulation).</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>stimulus_schedule_simulate.txt, stimulus_schedule_simul.txt</t>
-        </is>
-      </c>
+          <t>Schedule of the inference stimuli for the held-out cells (infer_test): test split and samples removed from the inference (perturbation_inference, remove_from_inference). Empty: the inference schedule.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
     </row>
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>perturbation_inference</t>
+          <t>stimulus_simulation_schedule</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Perturbations of the measured data, used by the inference: genetic perturbations of samples (KO / OV), and the inference stimuli (row sample_id = all: targets STIMk and effects on proliferation RATEk, k = column of stimulus_inference_schedule). Empty: one stimulus, every gene a possible target, no effect on the rates.</t>
+          <t>Schedules of the simulations, one row per simulated timepoint: inference stimuli (stimulus_k, acting on the genes and, through the RATEk of perturbation_inference, on proliferation and death), then perturbation stimuli (STIMk, as in perturbation_simulation).</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>KO_OV_inference.txt, stimulus_targets.txt/.csv</t>
+          <t>stimulus_schedule_simulate.txt, stimulus_schedule_simul.txt</t>
         </is>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>perturbation_simulation</t>
+          <t>perturbation_inference</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>In-silico perturbations simulated by simulate_network_KOV, one condition per row (add STIM2, STIM3... for several perturbation stimuli; their effects add up).</t>
+          <t>Perturbations of the measured data, used by the inference: genetic perturbations of samples (KO / OV), samples held out for validation (remove_from_inference, reference_sample), and the inference stimuli (row sample_id = all: targets STIMk and effects on proliferation RATEk, k = column of stimulus_inference_schedule). Empty: one stimulus, every gene a possible target, no effect on the rates.</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>KO_OV_Stim_simulate.txt, KO_OV_simulate.txt</t>
+          <t>KO_OV_inference.txt, stimulus_targets.txt/.csv</t>
         </is>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>times</t>
+          <t>perturbation_simulation</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Timepoints, one per row.</t>
+          <t>In-silico perturbations simulated by simulate_network_KOV, one condition per row (add STIM2, STIM3... for several perturbation stimuli; their effects add up).</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>times_to_inference.txt, times_to_simulate.txt</t>
+          <t>KO_OV_Stim_simulate.txt, KO_OV_simulate.txt</t>
         </is>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>proliferation_rates</t>
+          <t>times</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Anchors of the net proliferation rates per cell type (get_proliferation_rates); every cell type needs a value.</t>
+          <t>Timepoints, one per row.</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>proliferation_rates.txt/.csv</t>
+          <t>times_to_inference.txt, times_to_simulate.txt</t>
         </is>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>population_sizes</t>
+          <t>proliferation_rates</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Absolute population sizes, anchoring the growth estimated by optimal transport.</t>
+          <t>Anchors of the net proliferation rates per cell type (get_proliferation_rates); every cell type needs a value.</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>population_sizes.txt/.csv</t>
+          <t>proliferation_rates.txt/.csv</t>
         </is>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>population_sizes</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Absolute population sizes, anchoring the growth estimated by optimal transport.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>population_sizes.txt/.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>transition_rates</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Cell-type transition rate matrix constraining optimal transport: first column = source cell types, header = target cell types (as in obs cell_type_transition, else cell_type).</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>transition_rates.txt/.csv</t>
         </is>
@@ -938,6 +997,37 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>cell_type</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>net_rate_per_hour</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -968,7 +1058,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1676,20 +1766,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
+          <t>sample_id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
           <t>time</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>stimulus_1</t>
         </is>
@@ -1718,17 +1814,17 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
+          <t>sample_id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
           <t>time</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>stimulus_1</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>STIM1</t>
         </is>
       </c>
     </row>
@@ -1744,15 +1840,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1763,27 +1857,17 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>OV</t>
+          <t>stimulus_1</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
           <t>STIM1</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>RATE1</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>comment</t>
         </is>
       </c>
     </row>
@@ -1794,6 +1878,73 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>sample_id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>OV</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>remove_from_inference</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>reference_sample</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>STIM1</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>RATE1</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1842,7 +1993,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1871,35 +2022,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>cell_type</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>net_rate_per_hour</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
 </file>
--- a/CardamomOT_inputs.xlsx
+++ b/CardamomOT_inputs.xlsx
@@ -750,12 +750,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -775,222 +774,162 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Text files of older projects (genes_queries.txt, KO_OV_simulate.txt, stimulus_schedule.txt...) still present in Data/ are imported into this workbook at each run and OVERWRITE the corresponding cells (a warning is printed): delete them to edit the workbook instead.</t>
+          <t>Large numeric arrays stay files in Data/: reference_network.csv (structural prior), basal_init / basal_ref, inter_init / inter_ref (.npy or .csv), inter_simul_ref (.npy or .csv).</t>
         </is>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Large numeric arrays stay files in Data/: reference_network.csv (structural prior), basal_init / basal_ref, inter_init / inter_ref (.npy or .csv), inter_simul_ref (.npy or .csv).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="A4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Sheet</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Replaces (older text files)</t>
+          <t>model_parameters</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Parameters of the model for this project, grouped by use: empty value = default of CardamomOT/model/base.py; a filled value overrides it, and the command-line options override the workbook.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>model_parameters</t>
+          <t>gene_lists</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Parameters of the model for this project, grouped by use: empty value = default of CardamomOT/model/base.py; a filled value overrides it, and the command-line options override the workbook.</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
+          <t>Gene lists, one gene per row in each column. Any other column is a named gene list, usable as the targets (STIMk) or a RATE target of perturbation_inference and perturbation_simulation (exported as gene_list_&lt;name&gt;.txt).</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>gene_lists</t>
+          <t>stimulus_inference_schedule</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Gene lists, one gene per row in each column. Any other column is a named gene list, usable as the targets (STIMk) or a RATE target of perturbation_inference and perturbation_simulation (exported as gene_list_&lt;name&gt;.txt; legacy Data/gene_list_&lt;name&gt;.txt).</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>genes_queries.txt, proliferation_signatures.txt/.csv, death_signatures.txt/.csv, senescence_signatures.txt/.csv</t>
+          <t>Schedule of the stimuli of the measured data (inference); one row per timepoint, one column per stimulus (add stimulus_2, stimulus_3... for several stimuli; without this sheet: one stimulus). Rows with a sample_id give the schedule of that sample only (e.g. an untreated control at 0).</t>
         </is>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>stimulus_inference_schedule</t>
+          <t>stimulus_test_schedule</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Schedule of the stimuli of the measured data (inference); one row per timepoint, one column per stimulus (add stimulus_2, stimulus_3... for several stimuli; without this sheet: one stimulus). Rows with a sample_id give the schedule of that sample only (e.g. an untreated control at 0).</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>stimulus_schedule_inference.txt, stimulus_schedule.txt</t>
+          <t>Schedule of the inference stimuli for the held-out cells (infer_test): test split and samples removed from the inference (perturbation_inference, remove_from_inference). Empty: the inference schedule.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>stimulus_test_schedule</t>
+          <t>stimulus_simulation_schedule</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Schedule of the inference stimuli for the held-out cells (infer_test): test split and samples removed from the inference (perturbation_inference, remove_from_inference). Empty: the inference schedule.</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
+          <t>Schedules of the simulations, one row per simulated timepoint: inference stimuli (stimulus_k, acting on the genes and, through the RATEk of perturbation_inference, on proliferation and death), then perturbation stimuli (STIMk, as in perturbation_simulation).</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>stimulus_simulation_schedule</t>
+          <t>perturbation_inference</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Schedules of the simulations, one row per simulated timepoint: inference stimuli (stimulus_k, acting on the genes and, through the RATEk of perturbation_inference, on proliferation and death), then perturbation stimuli (STIMk, as in perturbation_simulation).</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>stimulus_schedule_simulate.txt, stimulus_schedule_simul.txt</t>
+          <t>Perturbations of the measured data, used by the inference: genetic perturbations of samples (KO / OV), samples held out for validation (remove_from_inference, reference_sample), and the inference stimuli (row sample_id = all: targets STIMk and effects on proliferation RATEk, k = column of stimulus_inference_schedule). Empty: one stimulus, every gene a possible target, no effect on the rates.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>perturbation_inference</t>
+          <t>perturbation_simulation</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Perturbations of the measured data, used by the inference: genetic perturbations of samples (KO / OV), samples held out for validation (remove_from_inference, reference_sample), and the inference stimuli (row sample_id = all: targets STIMk and effects on proliferation RATEk, k = column of stimulus_inference_schedule). Empty: one stimulus, every gene a possible target, no effect on the rates.</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>KO_OV_inference.txt, stimulus_targets.txt/.csv</t>
+          <t>In-silico perturbations simulated by simulate_network_KOV, one condition per row (add STIM2, STIM3... for several perturbation stimuli; their effects add up).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>perturbation_simulation</t>
+          <t>times</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>In-silico perturbations simulated by simulate_network_KOV, one condition per row (add STIM2, STIM3... for several perturbation stimuli; their effects add up).</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>KO_OV_Stim_simulate.txt, KO_OV_simulate.txt</t>
+          <t>Timepoints, one per row.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>times</t>
+          <t>proliferation_rates</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Timepoints, one per row.</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>times_to_inference.txt, times_to_simulate.txt</t>
+          <t>Anchors of the net proliferation rates per cell type (get_proliferation_rates); every cell type needs a value.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>proliferation_rates</t>
+          <t>population_sizes</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Anchors of the net proliferation rates per cell type (get_proliferation_rates); every cell type needs a value.</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>proliferation_rates.txt/.csv</t>
+          <t>Absolute population sizes, anchoring the growth estimated by optimal transport.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>population_sizes</t>
+          <t>transition_rates</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Absolute population sizes, anchoring the growth estimated by optimal transport.</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>population_sizes.txt/.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>transition_rates</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
           <t>Cell-type transition rate matrix constraining optimal transport: first column = source cell types, header = target cell types (as in obs cell_type_transition, else cell_type).</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>transition_rates.txt/.csv</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A2:C2"/>
+  <mergeCells count="3">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1167,7 +1106,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>literature prior cardamomOT/ref_network.csv: built by the gene selection if select_genes, else by build_reference_network</t>
+          <t>literature prior cardamomOT/ref_network.csv: built by the gene selection if select_genes, literature_selection and prior_network_pen = 0, else by build_reference_network</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1118,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>simulate_network_KOV + check_KOV_to_sim (Data/KO_OV_Stim_simulate)</t>
+          <t>simulate_network_KOV + check_KOV_to_sim (perturbation_simulation sheet)</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1199,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>at most this many genes of Data/genes_queries.txt (round robin over time/cell-type DE groups)</t>
+          <t>at most this many genes of genes_queries (gene_lists sheet) (round robin over time/cell-type DE groups)</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1316,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>reweight edge probabilities by OmniPath feasibility and write the literature prior (ref_network.csv)</t>
+          <t>gene selection: edge probabilities reweighted by OmniPath feasibility, whatever the prior</t>
         </is>
       </c>
     </row>
@@ -2002,19 +1941,19 @@
   <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>times_to_inference</t>
+          <t>times_inference</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>times_to_simulate</t>
+          <t>times_simulation</t>
         </is>
       </c>
     </row>

--- a/CardamomOT_inputs.xlsx
+++ b/CardamomOT_inputs.xlsx
@@ -207,6 +207,11 @@
         <t>Total population size at this timepoint</t>
       </text>
     </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional: dataset_id of the sample (empty or "all": default of the samples without rows)</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -455,6 +460,11 @@
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <t>Reference net proliferation rate (birth - death), in h^-1; without the inference stimulus if perturbation_inference gives its effect on this cell type (RATEk)</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional: dataset_id these anchors are for (empty or "all": default of the samples that have none of their own)</t>
       </text>
     </comment>
   </commentList>
@@ -941,11 +951,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -957,6 +968,11 @@
       <c r="B1" s="4" t="inlineStr">
         <is>
           <t>net_rate_per_hour</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>sample_id</t>
         </is>
       </c>
     </row>
@@ -972,11 +988,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -988,6 +1005,11 @@
       <c r="B1" s="4" t="inlineStr">
         <is>
           <t>population_size</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>sample_id</t>
         </is>
       </c>
     </row>

--- a/CardamomOT_inputs.xlsx
+++ b/CardamomOT_inputs.xlsx
@@ -204,7 +204,7 @@
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Total population size at this timepoint</t>
+        <t>Total population size at this timepoint (any unit: only the ratios between times of a sample are used)</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
@@ -224,7 +224,7 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Source cell type (rows) and target cell types (header): allowed transition rates</t>
+        <t>Source cell type (rows) and target cell types (header): transition rates in h^-1 (off-diagonal, 0 = no direct transition; diagonal ignored)</t>
       </text>
     </comment>
   </commentList>
@@ -239,7 +239,7 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Genes of interest for the gene selection (select_genes_and_split with select_genes = True), one per row</t>
+        <t>Genes of interest for the gene selection (select_genes with select_genes = True), one per row</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
@@ -319,22 +319,32 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Optional: dataset_id whose schedule these rows replace (empty or "all": default)</t>
+        <t>Optional: name of an alternative schedule of the simulations (empty: default schedule); perturbation_simulation chooses the scenarios of each condition (column schedules)</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Simulated timepoint (optional: without times, rows follow the sorted simulated timepoints)</t>
+        <t>Optional: dataset_id whose schedule these rows replace (empty or "all": default; default schedule only)</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
+        <t>Simulated timepoint; the value holds from this time on and applies to the simulated intervals ending after it (optional: without times, rows follow the sorted simulated timepoints)</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
         <t>Inference stimulus 1 during the simulations (default: its inference schedule)</t>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <t>Perturbation stimulus STIM1 of perturbation_simulation (default: 0 at the first time, 1 after)</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Free comment (ignored)</t>
       </text>
     </comment>
   </commentList>
@@ -419,6 +429,11 @@
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
+        <t>Schedules simulated for this condition, comma-separated: 'default' and/or scenario names of stimulus_simulation_schedule, 'all' = default + every scenario (empty: default)</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
         <t>Free comment (ignored)</t>
       </text>
     </comment>
@@ -459,12 +474,22 @@
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Reference net proliferation rate (birth - death), in h^-1; without the inference stimulus if perturbation_inference gives its effect on this cell type (RATEk)</t>
+        <t>Reference net proliferation rate (birth - death), in h^-1; without the inference stimulus if perturbation_inference gives its effect on this cell type (RATEk). May be left empty if birth and death are both given</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <t>Optional: dataset_id these anchors are for (empty or "all": default of the samples that have none of their own)</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional reference birth (division) rate, in h^-1: anchors the birth rate of the cells of this type (dilution of the proteins); with the net rate, gives the death rate</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional reference death rate, in h^-1: anchors the death rate of the cells of this type; with the net rate, gives the birth rate</t>
       </text>
     </comment>
   </commentList>
@@ -859,7 +884,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Schedules of the simulations, one row per simulated timepoint: inference stimuli (stimulus_k, acting on the genes and, through the RATEk of perturbation_inference, on proliferation and death), then perturbation stimuli (STIMk, as in perturbation_simulation).</t>
+          <t>Schedules of the simulations: inference stimuli (stimulus_k, acting on the genes and, through the RATEk of perturbation_inference, on proliferation and death), then perturbation stimuli (STIMk, as in perturbation_simulation). Rows with a scenario name give alternative schedules (e.g. alternating inference and perturbation stimuli), simulated for the conditions that ask for them; a value applies to the simulated intervals ending at or after its time, so switching times should be simulated times.</t>
         </is>
       </c>
     </row>
@@ -907,7 +932,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Anchors of the net proliferation rates per cell type (get_proliferation_rates); every cell type needs a value.</t>
+          <t>Anchors of the proliferation rates per cell type (fit_population_anchors, get_proliferation_rates); every cell type needs a net rate, given directly or as birth - death. Birth and death, when given, anchor the two rates separately; otherwise the change of the net rate is shared between them. Rows with a sample_id anchor that sample only (a sample with rows of its own ignores the default ones); a sample without anchors borrows those of the best-fitting sample.</t>
         </is>
       </c>
     </row>
@@ -919,7 +944,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Absolute population sizes, anchoring the growth estimated by optimal transport.</t>
+          <t>Population sizes per sample and time: they constrain the absolute growth in fit_population_anchors and in the growth estimated by optimal transport.</t>
         </is>
       </c>
     </row>
@@ -931,7 +956,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Cell-type transition rate matrix constraining optimal transport: first column = source cell types, header = target cell types (as in obs cell_type_transition, else cell_type).</t>
+          <t>Cell-type transition rate matrix (Markov generator) constraining optimal transport through the probabilities expm(Q dt): first column = source cell types, header = target cell types (as in obs cell_type_transition, else cell_type). To give a matrix per sample, add a column sample_id right of the matrix (one value per row of the block, or one block per sample); rows without sample_id are the default of the samples without block of their own.</t>
         </is>
       </c>
     </row>
@@ -951,12 +976,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -973,6 +1000,16 @@
       <c r="C1" s="4" t="inlineStr">
         <is>
           <t>sample_id</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>birth_rate_per_hour</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>death_rate_per_hour</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1087,289 +1124,292 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>estimate_proliferation_rates</t>
+          <t>CardamomOT_method</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>get_proliferation_rates: obs['proliferation_net_rate'] from gene signatures, anchored to Data/proliferation_rates</t>
+          <t>'temporal': current pipeline; 'stat': CardamomOT-stat (stationary snapshot per sample, times only for the mixture; automatic without obs['time']); 'stat+temporal': to be specified</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>simulate_with_proliferation</t>
+          <t>estimate_proliferation_rates</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>apply branching process in simulate_trajectories_unitary</t>
+          <t>get_proliferation_rates: obs['proliferation_net_rate'] from gene signatures, anchored to Data/proliferation_rates</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_genes</t>
+          <t>simulate_with_proliferation</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>select_genes_and_split: gene selection (queries, entropy genes, global network, Steiner tree); False = all genes kept</t>
+          <t>apply branching process in simulate_trajectories_unitary</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>build_prior_network</t>
+          <t>select_genes</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>literature prior cardamomOT/ref_network.csv: built by the gene selection if select_genes, literature_selection and prior_network_pen = 0, else by build_reference_network</t>
+          <t>select_genes (on the train cells of split_dataset): gene selection (queries, entropy genes, global network, Steiner tree); False = all genes kept</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>simulate_perturbations</t>
+          <t>build_prior_network</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>simulate_network_KOV + check_KOV_to_sim (perturbation_simulation sheet)</t>
+          <t>literature prior cardamomOT/ref_network.csv: built by the gene selection if select_genes, literature_selection and prior_network_pen = 0, else by build_reference_network</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>run_test</t>
+          <t>simulate_perturbations</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>infer_test + check_test_to_train on the held-out cells (needs split = 'train')</t>
+          <t>simulate_network_KOV + check_KOV_to_sim (perturbation_simulation sheet)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>split</t>
+          <t>run_test</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>'train': train/test split of the cells (train_rate per sample and time); 'full': all cells</t>
+          <t>infer_test + check_test_to_train on the held-out cells (needs split = 'train')</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>train_rate</t>
+          <t>run_classical_OT</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>share of the cells of each (sample, time) in the train split (at least 100); the test keeps at most as many</t>
+          <t>run_classical_OT: Waddington-OT-style analysis (every gene, train cells) before CardamomOT, 2 report pages</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>species</t>
+          <t>split</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>'auto' (from gene names), 'human' or 'mouse': degradation rates, proliferation signatures, literature prior</t>
+          <t>'train': train/test split of the cells (train_rate per sample and time); 'full': all cells</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Gene selection</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>train_rate</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>share of the cells of each (sample, time) in the train split (at least 100); the test keeps at most as many</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>num_max_genes</t>
+          <t>species</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>budget: number of selected genes (stimuli excluded)</t>
+          <t>'auto' (from gene names), 'human' or 'mouse': degradation rates, proliferation signatures, literature prior</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>n_query_genes</t>
+          <t>senescence_gating</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>at most this many genes of genes_queries (gene_lists sheet) (round robin over time/cell-type DE groups)</t>
+          <t>get_proliferation_rates: the senescence signature gates the proliferation score</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>n_entropy_genes</t>
+          <t>overwrite_degradation_rates</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>at least this many entropy genes (Gandrillon KD &amp; MDE), same round robin; n_query + n_entropy &lt; num_max_genes</t>
+          <t>get_degradation_rates: replace the d0/d1 already stored in the AnnData files</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>network_method</t>
+          <t>classical_ot_max_cells</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>global network: 'otvelo_granger', 'otvelo_corr', or &lt;project&gt;/network_methods/&lt;name&gt;.py</t>
+          <t>run_classical_OT: at most this many cells per (sample, time) in the couplings (others: kernel regression)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>k_in_steiner</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>strongest incoming edges kept per gene in the Steiner graph</t>
-        </is>
-      </c>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Gene selection</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>closure_min</t>
+          <t>num_max_genes</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>closure: add the gene bringing the most probable regulation (sum of w) to the selection while &gt;= this</t>
+          <t>budget: number of selected genes (stimuli excluded)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>min_entropy_change</t>
+          <t>n_query_genes</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>variability floor of the selection: max BUB-entropy change between consecutive times (bits, Gandrillon MDE)</t>
+          <t>at most this many genes of genes_queries (gene_lists sheet) (round robin over time/cell-type DE groups)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>min_nb_separation</t>
+          <t>n_entropy_genes</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>... and separation of the extreme NB modes at the mixture initialization (times / cell types, batch_size_mixture cells per time)</t>
+          <t>at least this many entropy genes (Gandrillon KD &amp; MDE), same round robin; n_query + n_entropy &lt; num_max_genes</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Literature prior network</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>network_method</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>global network: 'otvelo_granger', 'otvelo_corr', 'wot_granger' (through the run_classical_OT couplings), or &lt;project&gt;/network_methods/&lt;name&gt;.py</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>prior_network_pen</t>
+          <t>sample_network_combination</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>1 if we don't use prior information. If not we can penalize the non-existing age in prior network with values between 1 and 0: 0 = impossible edge</t>
+          <t>several samples, gene selection: 'consensus' (edge probabilities averaged, shared network), 'any' (probabilistic OR + closure balanced over the samples, independent condition networks); 'auto' = 'any' with &gt;= 2 network conditions and network_condition_pen = 0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>max_free_params</t>
+          <t>k_in_steiner</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>change=1 with ref=1 and prior 0 (hard prior): gene budget set so that the literature prior leaves this many free network parameters</t>
+          <t>strongest incoming edges kept per gene in the Steiner graph</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>literature_selection</t>
+          <t>closure_min</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>gene selection: edge probabilities reweighted by OmniPath feasibility, whatever the prior</t>
+          <t>closure: add the gene bringing the most probable regulation (sum of w) to the selection while &gt;= this</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>literature_depth</t>
+          <t>min_entropy_change</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>max path length in the literature graph (last edge TF -&gt; target)</t>
+          <t>variability floor of the selection: max BUB-entropy change between consecutive times (bits, Gandrillon MDE)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>literature_resources</t>
+          <t>min_nb_separation</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>'extended' (OmniPath, CollecTRI + PathwayExtra, KinaseExtra, LigRecExtra, DoRothEA A-D, TFtarget) or 'core' (OmniPath + CollecTRI)</t>
+          <t>... and separation of the extreme NB modes at the mixture initialization (times / cell types, batch_size_mixture cells per time)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Stimulus</t>
+          <t>Literature prior network</t>
         </is>
       </c>
       <c r="B27" s="6" t="n"/>
@@ -1378,88 +1418,88 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>stimulus</t>
+          <t>prior_network_pen</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>1 if we simulate with a stimulus. If not we can penalize the stimulus with a value between 1 and 0: 0 = no sitmulus</t>
+          <t>1 if we don't use prior information. If not we can penalize the non-existing age in prior network with values between 1 and 0: 0 = impossible edge</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Per-cell sequencing depth</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>max_free_params</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>change=1 with ref=1 and prior 0 (hard prior): gene budget set so that the literature prior leaves this many free network parameters</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>use_depth_factor</t>
+          <t>literature_selection</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>use obs['depth_factor'] (estimate_cell_depth) in the NB model and simulations; False = s_i = 1 (an existing factor is kept but ignored)</t>
+          <t>gene selection: edge probabilities reweighted by OmniPath feasibility, whatever the prior</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>compute_depth_factor</t>
+          <t>literature_depth</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>estimate_cell_depth computes the diagnostic and writes obs['depth_factor'] if needed; False = only reads an existing factor (never removed)</t>
+          <t>max path length in the literature graph (last edge TF -&gt; target)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>allow_depth_correction</t>
+          <t>literature_resources</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>estimate_cell_depth: apply the per-cell depth factor s_i when the diagnostic recommends it</t>
+          <t>'extended' (OmniPath, CollecTRI + PathwayExtra, KinaseExtra, LigRecExtra, DoRothEA A-D, TFtarget) or 'core' (OmniPath + CollecTRI)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>depth_method</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>depth factor: 'group_median', 'poissonian' (Fang &amp; Pachter, 2025), or &lt;project&gt;/depth_methods/&lt;name&gt;.py</t>
-        </is>
-      </c>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Stimulus</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>depth_by_cell_type</t>
+          <t>stimulus</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>estimate s_i within (sample, time, cell type) groups; False = (sample, time) only:</t>
+          <t>1 if we simulate with a stimulus. If not we can penalize the stimulus with a value between 1 and 0: 0 = no sitmulus</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>NB mixture and samples</t>
+          <t>Per-cell sequencing depth</t>
         </is>
       </c>
       <c r="B35" s="6" t="n"/>
@@ -1468,67 +1508,67 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>mean_forcing_em</t>
+          <t>use_depth_factor</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>at which point we force the mean correction: the higher the more</t>
+          <t>use obs['depth_factor'] (estimate_cell_depth) in the NB model and simulations; False = s_i = 1 (an existing factor is kept but ignored)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>batch_size_mixture</t>
+          <t>compute_depth_factor</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Maximum number of cells per time used for mixture calibration in the inference.</t>
+          <t>estimate_cell_depth computes the diagnostic and writes obs['depth_factor'] if needed; False = only reads an existing factor (never removed)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>soft_em_refinement</t>
+          <t>allow_depth_correction</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>NB mixture: refine (ks, c) by soft EM with fixed basin masses</t>
+          <t>estimate_cell_depth: apply the per-cell depth factor s_i when the diagnostic recommends it</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>integrate_samples</t>
+          <t>depth_method</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>in [0, 1]: per-sample mixtures pushed towards the common target (1 = equal parameters, 0 = own fits)</t>
+          <t>depth factor: 'group_median', 'poissonian' (Fang &amp; Pachter, 2025), or &lt;project&gt;/depth_methods/&lt;name&gt;.py</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ref_sample_integration</t>
+          <t>depth_by_cell_type</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>dataset_id of the reference sample; None = cell-weighted average of mode means (keeps total counts)</t>
+          <t>estimate s_i within (sample, time, cell type) groups; False = (sample, time) only:</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Network inference</t>
+          <t>NB mixture and samples</t>
         </is>
       </c>
       <c r="B41" s="6" t="n"/>
@@ -1537,136 +1577,346 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>force_basins</t>
+          <t>mean_forcing_em</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Do we want to ensure the means to be preserved by the NB mixture ? It may not preserve multistability</t>
+          <t>at which point we force the mean correction: the higher the more</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>temporal_basins</t>
+          <t>batch_size_mixture</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Is it preserved temporally ?</t>
+          <t>Maximum number of cells per time used for mixture calibration in the inference.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>min_n_loops</t>
+          <t>soft_em_refinement</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>minimal number of iterations in inference loops</t>
+          <t>NB mixture: refine (ks, c) by soft EM with fixed basin masses</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>max_iter</t>
+          <t>integrate_samples</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>max iteration for main loop</t>
+          <t>in [0, 1]: per-sample mixtures pushed towards the common target (1 = equal parameters, 0 = own fits)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>batch_size_traj</t>
+          <t>ref_sample_integration</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Maximum number of cells used per time point per sample for solving EOT problems in the inference.</t>
+          <t>dataset_id of the reference sample; None = cell-weighted average of mode means (keeps total counts)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>n_network_fits</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Theta = mean of min(n_network_fits, 1 + n_states // batch_size) fits on disjoint subsamples, at every network update</t>
-        </is>
-      </c>
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Network inference</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>Proliferation and simulation</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="n"/>
-      <c r="C48" s="6" t="n"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>force_basins</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Do we want to ensure the means to be preserved by the NB mixture ? It may not preserve multistability</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>growth_reg_source</t>
+          <t>temporal_basins</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>source-marginal relaxation (x log G) of the growth OT pass: small = data-driven but noisy, large = prior kept</t>
+          <t>Is it preserved temporally ?</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>prolif_uses_stimulus</t>
+          <t>min_n_loops</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>inference stimuli are inputs of the ProliferationMLP, R(u, P) (no effect if constant over the intervals)</t>
+          <t>minimal number of iterations in inference loops</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>simulation_stochastic</t>
+          <t>max_iter</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>1 if we simulate Bursty-like proteins, 0 if deterministic limit for proteins</t>
+          <t>max iteration for main loop</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>Reproducibility</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="n"/>
-      <c r="C52" s="6" t="n"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>batch_size_traj</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Maximum number of cells used per time point per sample for solving EOT problems in the inference.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>n_network_fits</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Theta = mean of min(n_network_fits, 1 + n_states // batch_size) fits on disjoint subsamples, at every network update</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>constrain_basal_uniform</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>&gt;= 0 penalty strength that pushes per-sample basals to be equal (ignores samples pinned by KO/OV basal_ref)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>network_condition_pen</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>&gt;= 0, with &gt;= 2 values of obs['network_condition']: fused L1 penalty on the deviations of each condition's network from the shared one, relative to the sparsity penalty (large = common network, 0 = independent networks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Proliferation and simulation</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="n"/>
+      <c r="C56" s="6" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>growth_reg_source</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>source-marginal relaxation (x log G) of the growth OT pass: small = data-driven but noisy, large = prior kept</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>prolif_uses_stimulus</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>inference stimuli are inputs of the ProliferationMLP, R(u, P) (no effect if constant over the intervals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>simulation_stochastic</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>1 if we simulate Bursty-like proteins, 0 if deterministic limit for proteins</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>simulate_full_with_harissa</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>use Harissa PDMP to jointly simulate proteins+mRNAs (simulations only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>protein_dilution</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>proteins diluted at the birth rate b of each cell: dP/dt = d1 u - (d1 + b) P (obs['proliferation_birth_rate']; independent of simulate_with_proliferation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>classifier_method</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>cell types of the model outputs (report, notebooks): 'random_forest' or 'logistic'</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>embedding_method_visualization</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>report: 2-D embeddings with 'umap', 'pca' or 'phate'</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>cell_depth_for_representation</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>report, cell-type classifiers: mRNA / depth factor (if computed), model draws at the reference depth; False = raw counts, draws at the cells' depth</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>report_net_index</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>report: network shown when n_networks &gt; 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>report_normalize</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>report UMAPs: counts normalised per cell</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>report_log1p</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>report UMAPs: log1p of the counts</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>report_n_umap</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>report: maximal number of cells per stage in the UMAPs (0 = all)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>Reproducibility</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="6" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Random seed for reproducibility (main process and parallel workers); None = not seeded (runs vary)</t>
         </is>
@@ -1801,34 +2051,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
           <t>sample_id</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>stimulus_1</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>STIM1</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
     </row>
@@ -1911,7 +2173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1919,6 +2181,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1943,6 +2206,11 @@
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>schedules</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>comment</t>
         </is>

--- a/CardamomOT_inputs.xlsx
+++ b/CardamomOT_inputs.xlsx
@@ -1087,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1856,67 +1856,55 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>report_net_index</t>
+          <t>report_normalize</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>report: network shown when n_networks &gt; 1</t>
+          <t>report UMAPs: counts normalised per cell</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>report_normalize</t>
+          <t>report_log1p</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>report UMAPs: counts normalised per cell</t>
+          <t>report UMAPs: log1p of the counts</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>report_log1p</t>
+          <t>report_n_umap</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>report UMAPs: log1p of the counts</t>
+          <t>report: maximal number of cells per stage in the UMAPs (0 = all)</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>report_n_umap</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>report: maximal number of cells per stage in the UMAPs (0 = all)</t>
-        </is>
-      </c>
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Reproducibility</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="6" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>Reproducibility</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="n"/>
-      <c r="C70" s="6" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Random seed for reproducibility (main process and parallel workers); None = not seeded (runs vary)</t>
         </is>

--- a/CardamomOT_inputs.xlsx
+++ b/CardamomOT_inputs.xlsx
@@ -1787,12 +1787,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>simulate_full_with_harissa</t>
+          <t>simulation_mrnas_direct</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>use Harissa PDMP to jointly simulate proteins+mRNAs (simulations only)</t>
+          <t>True: the PDMP simulations carry explicit mRNA (mRNA bursts, proteins translated from them) and return mRNA counts; the inference then fits the degradations for that model (mRNA-driven proteins, two-stage noise). The ODE (simulation_stochastic = 0) stays on the proteins</t>
         </is>
       </c>
     </row>

--- a/CardamomOT_inputs.xlsx
+++ b/CardamomOT_inputs.xlsx
@@ -455,6 +455,11 @@
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <t>Timepoints of the simulations (0 added if absent)</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Timepoints of the test cells (split = train; 0 added if absent): times beyond the inference ones are held out for the test only; empty = the inference timepoints</t>
       </text>
     </comment>
   </commentList>
@@ -2216,11 +2221,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2232,6 +2238,11 @@
       <c r="B1" s="4" t="inlineStr">
         <is>
           <t>times_simulation</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>times_test</t>
         </is>
       </c>
     </row>

--- a/CardamomOT_inputs.xlsx
+++ b/CardamomOT_inputs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eventre/Documents/GitHub/CardamomOT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F874597B-403D-AB40-9FF9-AA8FB50B5740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC103DA2-89D0-CC48-A128-7ECEA4C3388F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2954,7 +2954,7 @@
         <v>207</v>
       </c>
       <c r="B95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>208</v>

--- a/CardamomOT_inputs.xlsx
+++ b/CardamomOT_inputs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eventre/Documents/GitHub/CardamomOT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC103DA2-89D0-CC48-A128-7ECEA4C3388F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76077CF6-1E27-8B45-8EC8-550A3C8D55BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2679,7 +2679,7 @@
         <v>151</v>
       </c>
       <c r="B65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>152</v>
